--- a/backend/tests/test_files/test_patient.xlsx
+++ b/backend/tests/test_files/test_patient.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="P001" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="P002" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="protocole" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,35 +27,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002C3E50"/>
-        <bgColor rgb="002C3E50"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EBF5FB"/>
-        <bgColor rgb="00EBF5FB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FDFEFE"/>
-        <bgColor rgb="00FDFEFE"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -69,13 +48,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -443,162 +417,156 @@
   </sheetPr>
   <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>patient_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>session</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>exercise</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>P001</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Seance 1</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>2026-01-10</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Verrouillage genou aux barres paralleles avec aide</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>P001</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Seance 1</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>2026-01-10</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Transfer fauteuil roulant plan bobhate avec aide allegement de poids</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>P001</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Seance 1</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>2026-01-10</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Push-up en position semi-allongee 3 series de 10 repetitions</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>P001</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Seance 2</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>2026-01-17</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Marche avec deambulateur 10 minutes</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>P001</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Seance 2</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>2026-01-17</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Exercice equilibre unipodal barre fixe 30 secondes chaque cote</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>P001</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Seance 2</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>2026-01-17</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Etirement ischio-jambiers position allongee</t>
         </is>
@@ -617,120 +585,176 @@
   </sheetPr>
   <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>patient_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>session</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>exercise</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>P002</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Seance 1</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>2026-01-12</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Renforcement biceps avec elastique 3x15</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>P002</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Seance 1</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>2026-01-12</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Transfer lit fauteuil avec aide partielle</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>P002</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Seance 2</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>2026-01-19</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Squat partiel avec appui mural 10 repetitions</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>P002</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Seance 2</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>2026-01-19</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Exercice respiration diaphragmatique 5 minutes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>champ</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>valeur</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>protocole</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Rééducation neurologique post-AVC phase subaiguë</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>obj_principal</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>FUNC</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>obj_secondaires</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>STR, LOAD</t>
         </is>
       </c>
     </row>
